--- a/data/RV empurrada.xlsx
+++ b/data/RV empurrada.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\Infos PG empurrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FD2E4D-523C-4B07-ADBD-B39F89BEF2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F982FA3B-71DB-462C-B9EE-473B16A2F6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RV" sheetId="1" r:id="rId1"/>
+    <sheet name="RV empurrada" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="113">
   <si>
     <t>Rubrica</t>
   </si>
@@ -55,9 +55,6 @@
     <t>Proventos</t>
   </si>
   <si>
-    <t>Descontos</t>
-  </si>
-  <si>
     <t>PRÊMIO DE PRODUTIVIDADE</t>
   </si>
   <si>
@@ -302,6 +299,66 @@
   </si>
   <si>
     <t>28/08/2021</t>
+  </si>
+  <si>
+    <t>ALBERT LEONARDO SOUZA E SILVA</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>ANDERSON MOREIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>16/09/2020</t>
+  </si>
+  <si>
+    <t>CIRO AFONSO DOMINGOS</t>
+  </si>
+  <si>
+    <t>MOTORISTA CARRETA SEMI-REBOQUE [LOND]</t>
+  </si>
+  <si>
+    <t>15/09/2021</t>
+  </si>
+  <si>
+    <t>EDSON DOTTI</t>
+  </si>
+  <si>
+    <t>01/11/2023</t>
+  </si>
+  <si>
+    <t>GEOVANE MACHADO DE PAULA</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>MARCELO DA SILVA GOES</t>
+  </si>
+  <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
+    <t>MARCIO MARKS</t>
+  </si>
+  <si>
+    <t>03/12/2020</t>
+  </si>
+  <si>
+    <t>NEIVERTON LUIZ DA ROCHA</t>
+  </si>
+  <si>
+    <t>TIAGO RIBEIRO CUNHA</t>
+  </si>
+  <si>
+    <t>VLAUMIR BENTO ARCADI</t>
+  </si>
+  <si>
+    <t>06/07/2023</t>
+  </si>
+  <si>
+    <t>Data</t>
   </si>
 </sst>
 </file>
@@ -353,11 +410,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.88671875" bestFit="1" customWidth="1"/>
@@ -712,7 +770,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -720,1326 +778,2736 @@
         <v>1068</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>90691</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1">
         <v>668.52716545454541</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="L2" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1068</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2">
         <v>90177</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2">
         <v>210.6304943181818</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1068</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>90500</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1">
         <v>3667.65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1">
         <v>368.59272954545457</v>
       </c>
-      <c r="L4" s="1"/>
+      <c r="L4" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1068</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
         <v>90997</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2">
         <v>153.6093465909091</v>
       </c>
-      <c r="L5" s="2"/>
+      <c r="L5" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1068</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>90774</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
         <v>97.111295454545456</v>
       </c>
-      <c r="L6" s="1"/>
+      <c r="L6" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1068</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2">
         <v>90940</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2">
         <v>105.4764820454545</v>
       </c>
-      <c r="L7" s="2"/>
+      <c r="L7" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1068</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>99163</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
         <v>287.66586340909089</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1068</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2">
         <v>90757</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2">
         <v>652.3957032954545</v>
       </c>
-      <c r="L9" s="2"/>
+      <c r="L9" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1068</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>90402</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
         <v>209.48747727272729</v>
       </c>
-      <c r="L10" s="1"/>
+      <c r="L10" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1068</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2">
         <v>90787</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2">
         <v>184.66889204545461</v>
       </c>
-      <c r="L11" s="2"/>
+      <c r="L11" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1068</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="1">
         <v>90172</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="H12" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
         <v>142.93377840909091</v>
       </c>
-      <c r="L12" s="1"/>
+      <c r="L12" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1068</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2">
         <v>90082</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2">
         <v>21.33702693181818</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1068</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1">
         <v>90988</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
         <v>22.64861340909091</v>
       </c>
-      <c r="L14" s="1"/>
+      <c r="L14" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>1068</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2">
         <v>90474</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2">
         <v>156.81858522727271</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1068</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>90858</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
         <v>169.08767875000001</v>
       </c>
-      <c r="L16" s="1"/>
+      <c r="L16" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>1068</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2">
         <v>909106</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2">
         <v>280.20534090909092</v>
       </c>
-      <c r="L17" s="2"/>
+      <c r="L17" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1068</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="1">
         <v>99177</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
         <v>35.895380681818182</v>
       </c>
-      <c r="L18" s="1"/>
+      <c r="L18" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>1068</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2">
         <v>60579</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2">
         <v>3325.61</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2">
         <v>29.04680420454546</v>
       </c>
-      <c r="L19" s="2"/>
+      <c r="L19" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1068</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1">
         <v>90845</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1">
         <v>3285.27</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
         <v>170.7023681818182</v>
       </c>
-      <c r="L20" s="1"/>
+      <c r="L20" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>1068</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" s="2">
         <v>90992</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2">
         <v>3285.27</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2">
         <v>280.90649568181823</v>
       </c>
-      <c r="L21" s="2"/>
+      <c r="L21" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>1068</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1">
         <v>90264</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
         <v>30.863659090909099</v>
       </c>
-      <c r="L22" s="1"/>
+      <c r="L22" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>1068</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="2">
         <v>90442</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2">
         <v>47.233164772727278</v>
       </c>
-      <c r="L23" s="2"/>
+      <c r="L23" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>1068</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>90472</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
         <v>360.72453977272733</v>
       </c>
-      <c r="L24" s="1"/>
+      <c r="L24" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>1068</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" s="2">
         <v>90708</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2">
         <v>80.799708977272729</v>
       </c>
-      <c r="L25" s="2"/>
+      <c r="L25" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>1068</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1">
         <v>90777</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1">
         <v>3171.33</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
         <v>660.72939215909093</v>
       </c>
-      <c r="L26" s="1"/>
+      <c r="L26" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>1068</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="2">
         <v>10383</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2">
         <v>3285.27</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2">
         <v>46.317308295454538</v>
       </c>
-      <c r="L27" s="2"/>
+      <c r="L27" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>1068</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="1">
         <v>90163</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
         <v>270.95243079545457</v>
       </c>
-      <c r="L28" s="1"/>
+      <c r="L28" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>1068</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" s="2">
         <v>90424</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2">
         <v>36.734244545454537</v>
       </c>
-      <c r="L29" s="2"/>
+      <c r="L29" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>1068</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1">
         <v>90201</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1">
         <v>3285.27</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1">
         <v>103.9543664772727</v>
       </c>
-      <c r="L30" s="1"/>
+      <c r="L30" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>1068</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="2">
         <v>90430</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H31" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2">
         <v>90.938406931818179</v>
       </c>
-      <c r="L31" s="2"/>
+      <c r="L31" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>1068</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32" s="1">
         <v>90212</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H32" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
         <v>201.76293749999999</v>
       </c>
-      <c r="L32" s="1"/>
+      <c r="L32" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>1068</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" s="2">
         <v>90825</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2">
         <v>135.80543045454539</v>
       </c>
-      <c r="L33" s="2"/>
+      <c r="L33" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>1068</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1">
         <v>90819</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
         <v>209.72120170454551</v>
       </c>
-      <c r="L34" s="1"/>
+      <c r="L34" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>1068</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" s="2">
         <v>90180</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H35" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2">
         <v>390.20534090909092</v>
       </c>
-      <c r="L35" s="2"/>
+      <c r="L35" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>1068</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1">
         <v>909104</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1">
         <v>3171.33</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
         <v>230.25689340909091</v>
       </c>
-      <c r="L36" s="1"/>
+      <c r="L36" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>1068</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" s="2">
         <v>90435</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2">
         <v>55.333576931818193</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>1068</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" s="1">
         <v>90995</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H38" s="1">
         <v>3285.27</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>200.85307329545449</v>
       </c>
-      <c r="L38" s="1"/>
+      <c r="L38" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>1068</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" s="2">
         <v>90139</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="2">
-        <v>3171.33</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2">
         <v>185.6583181818182</v>
       </c>
-      <c r="L39" s="2"/>
+      <c r="L39" s="4">
+        <v>46023</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>1068</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1">
         <v>90267</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="1">
-        <v>3171.33</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>255.41587000000001</v>
       </c>
-      <c r="L40" s="1"/>
+      <c r="L40" s="4">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="1">
+        <v>90691</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1">
+        <v>1159.6816064860141</v>
+      </c>
+      <c r="L41" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="2">
+        <v>90177</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
+        <v>7.4991181031468548</v>
+      </c>
+      <c r="L42" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="1">
+        <v>90500</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="1">
+        <v>3667.65</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1">
+        <v>245.31149252622379</v>
+      </c>
+      <c r="L43" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="2">
+        <v>99135</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2">
+        <v>62.353408216783222</v>
+      </c>
+      <c r="L44" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="1">
+        <v>90186</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1">
+        <v>179.06223090034959</v>
+      </c>
+      <c r="L45" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="2">
+        <v>99163</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2">
+        <v>113.0626571940559</v>
+      </c>
+      <c r="L46" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="1">
+        <v>90274</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="1">
+        <v>3190</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1">
+        <v>144.77375000000001</v>
+      </c>
+      <c r="L47" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="2">
+        <v>90656</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
+        <v>70.624491110139857</v>
+      </c>
+      <c r="L48" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="1">
+        <v>90787</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1">
+        <v>95.833953234265735</v>
+      </c>
+      <c r="L49" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="2">
+        <v>90172</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H50" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2">
+        <v>22.30615621503496</v>
+      </c>
+      <c r="L50" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="1">
+        <v>90082</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1">
+        <v>10.876332167832169</v>
+      </c>
+      <c r="L51" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="2">
+        <v>90988</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>82.697011678321687</v>
+      </c>
+      <c r="L52" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="1">
+        <v>90474</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1">
+        <v>663.86220585664341</v>
+      </c>
+      <c r="L53" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="2">
+        <v>90858</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2">
+        <v>297.51945498251752</v>
+      </c>
+      <c r="L54" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="1">
+        <v>909106</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1">
+        <v>133.7102854020979</v>
+      </c>
+      <c r="L55" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="2">
+        <v>90980</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="2">
+        <v>3285.27</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2">
+        <v>95.995614484265744</v>
+      </c>
+      <c r="L56" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="1">
+        <v>99177</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1">
+        <v>78.889120979020987</v>
+      </c>
+      <c r="L57" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="2">
+        <v>90845</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2">
+        <v>3285.27</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2">
+        <v>321.25979763986021</v>
+      </c>
+      <c r="L58" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="1">
+        <v>90264</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1">
+        <v>178.01065734265731</v>
+      </c>
+      <c r="L59" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="2">
+        <v>90472</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2">
+        <v>479.28624562937063</v>
+      </c>
+      <c r="L60" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="1">
+        <v>90708</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1">
+        <v>104.71071169580421</v>
+      </c>
+      <c r="L61" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="2">
+        <v>90777</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2">
+        <v>498.93533655594399</v>
+      </c>
+      <c r="L62" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="1">
+        <v>90427</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1">
+        <v>58.657249125874117</v>
+      </c>
+      <c r="L63" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="2">
+        <v>10383</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2">
+        <v>3285.27</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2">
+        <v>13.54221064685315</v>
+      </c>
+      <c r="L64" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="1">
+        <v>90163</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1">
+        <v>121.3731850524476</v>
+      </c>
+      <c r="L65" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="2">
+        <v>90424</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2">
+        <v>3.056872919580421</v>
+      </c>
+      <c r="L66" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="1">
+        <v>90226</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1">
+        <v>94.572491258741266</v>
+      </c>
+      <c r="L67" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="2">
+        <v>90760</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2">
+        <v>413.8198269230769</v>
+      </c>
+      <c r="L68" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="1">
+        <v>90430</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1">
+        <v>178.66534870629371</v>
+      </c>
+      <c r="L69" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="2">
+        <v>90212</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2">
+        <v>145.489923479021</v>
+      </c>
+      <c r="L70" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="1">
+        <v>90180</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1">
+        <v>152.43469711538461</v>
+      </c>
+      <c r="L71" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="2">
+        <v>909104</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2">
+        <v>3171.33</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2">
+        <v>277.99762607517482</v>
+      </c>
+      <c r="L72" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="1">
+        <v>90435</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1">
+        <v>142.0481045891608</v>
+      </c>
+      <c r="L73" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="2">
+        <v>90995</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="2">
+        <v>3285.27</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2">
+        <v>296.23055948426571</v>
+      </c>
+      <c r="L74" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="1">
+        <v>99176</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1">
+        <v>93.682032779720288</v>
+      </c>
+      <c r="L75" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="2">
+        <v>90496</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="2">
+        <v>3667.65</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2">
+        <v>227.93890323426569</v>
+      </c>
+      <c r="L76" s="4">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="1">
+        <v>90267</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="1">
+        <v>3171.33</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1">
+        <v>369.24837208916091</v>
+      </c>
+      <c r="L77" s="4">
+        <v>46054</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
